--- a/RPOTA.xlsx
+++ b/RPOTA.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="38">
   <si>
     <t/>
   </si>
   <si>
-    <t>20118154</t>
-  </si>
-  <si>
-    <t>ROLL PLASTIK BUAH</t>
+    <t>20118157</t>
+  </si>
+  <si>
+    <t>ROLL STRUK EDC BCA</t>
   </si>
   <si>
     <t>RPOTA</t>
@@ -28,15 +28,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20118157</t>
-  </si>
-  <si>
-    <t>ROLL STRUK EDC BCA</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -100,6 +91,15 @@
     <t>17</t>
   </si>
   <si>
+    <t>20136561</t>
+  </si>
+  <si>
+    <t>APRICOT KARET GELANG</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>20054963</t>
   </si>
   <si>
@@ -116,6 +116,15 @@
   </si>
   <si>
     <t>20</t>
+  </si>
+  <si>
+    <t>20128131</t>
+  </si>
+  <si>
+    <t>ROLL BUAH SEAL 8CM</t>
+  </si>
+  <si>
+    <t>21</t>
   </si>
 </sst>
 </file>
@@ -508,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -538,7 +547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -554,25 +563,28 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -592,15 +604,15 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -609,13 +621,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -631,8 +640,11 @@
       <c r="E6" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -647,9 +659,6 @@
       </c>
       <c r="E7" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -703,7 +712,7 @@
         <v>31</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -723,7 +732,27 @@
         <v>34</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
